--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:44:54+00:00</t>
+    <t>2023-05-08T13:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T13:51:23+00:00</t>
+    <t>2023-05-08T14:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="417">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -271,6 +271,9 @@
     <t>Organization(classCode=ORG, determinerCode=INST)</t>
   </si>
   <si>
+    <t>administrative.group</t>
+  </si>
+  <si>
     <t>Organization.id</t>
   </si>
   <si>
@@ -354,7 +357,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -412,6 +415,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -452,7 +459,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -512,205 +519,199 @@
     <t>Organization.identifier.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.system</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.version</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.version</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.system</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.version</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.version</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -892,7 +893,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -1179,6 +1180,10 @@
   </si>
   <si>
     <t>Need to keep track of assigned contact points within bigger organization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>.contactParty</t>
@@ -1628,7 +1633,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.10546875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="43.6484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -1876,15 +1881,15 @@
         <v>30</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1895,7 +1900,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>77</v>
@@ -1904,19 +1909,19 @@
         <v>77</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1966,13 +1971,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -1995,10 +2000,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2009,7 +2014,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>77</v>
@@ -2018,16 +2023,16 @@
         <v>77</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2078,19 +2083,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2107,10 +2112,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2121,28 +2126,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2192,19 +2197,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2221,10 +2226,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2235,7 +2240,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2247,16 +2252,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2282,13 +2287,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2306,19 +2311,19 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2335,21 +2340,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2361,16 +2366,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2420,25 +2425,25 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2449,14 +2454,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2475,16 +2480,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2534,7 +2539,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2546,13 +2551,13 @@
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2563,14 +2568,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2589,16 +2594,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2648,7 +2653,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2660,13 +2665,13 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2677,14 +2682,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2697,25 +2702,25 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2764,7 +2769,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2776,13 +2781,13 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2793,10 +2798,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2804,7 +2809,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>79</v>
@@ -2816,20 +2821,20 @@
         <v>77</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2866,19 +2871,19 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2887,43 +2892,43 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
@@ -2932,20 +2937,20 @@
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2994,7 +2999,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3003,30 +3008,30 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3037,7 +3042,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
@@ -3049,13 +3054,13 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3106,13 +3111,13 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>77</v>
@@ -3124,7 +3129,7 @@
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3135,14 +3140,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3161,16 +3166,16 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3208,19 +3213,19 @@
         <v>77</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3232,13 +3237,13 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3249,10 +3254,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3263,31 +3268,31 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3312,11 +3317,9 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y15" t="s" s="2">
         <v>179</v>
       </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
         <v>180</v>
       </c>
@@ -3342,16 +3345,16 @@
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>182</v>
@@ -3379,7 +3382,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
@@ -3388,7 +3391,7 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>185</v>
@@ -3430,44 +3433,42 @@
       <c r="X16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Y16" s="2"/>
+      <c r="Z16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF16" t="s" s="2">
+      <c r="AG16" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK16" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>182</v>
@@ -3481,10 +3482,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3495,7 +3496,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3507,13 +3508,13 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3564,13 +3565,13 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
@@ -3582,7 +3583,7 @@
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3593,14 +3594,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3619,16 +3620,16 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3666,19 +3667,19 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3690,13 +3691,13 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3707,10 +3708,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3730,22 +3731,22 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3794,7 +3795,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3806,13 +3807,13 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3823,10 +3824,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3837,7 +3838,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -3849,13 +3850,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3906,13 +3907,13 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
@@ -3924,7 +3925,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3935,14 +3936,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3961,16 +3962,16 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4008,19 +4009,19 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4032,13 +4033,13 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -4049,10 +4050,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4063,7 +4064,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -4072,22 +4073,22 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4097,64 +4098,64 @@
         <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="T22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF22" t="s" s="2">
+      <c r="AG22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AG22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK22" t="s" s="2">
+      <c r="AL22" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4165,10 +4166,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4179,7 +4180,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -4188,10 +4189,10 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>225</v>
@@ -4256,13 +4257,13 @@
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>229</v>
@@ -4293,7 +4294,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4302,10 +4303,10 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>233</v>
@@ -4370,13 +4371,13 @@
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>238</v>
@@ -4407,7 +4408,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4416,10 +4417,10 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>242</v>
@@ -4484,13 +4485,13 @@
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>247</v>
@@ -4521,7 +4522,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4530,7 +4531,7 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>251</v>
@@ -4600,13 +4601,13 @@
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>257</v>
@@ -4637,7 +4638,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4646,10 +4647,10 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>261</v>
@@ -4716,13 +4717,13 @@
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>267</v>
@@ -4750,10 +4751,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4762,10 +4763,10 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>271</v>
@@ -4832,13 +4833,13 @@
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>278</v>
@@ -4866,10 +4867,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -4878,10 +4879,10 @@
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>283</v>
@@ -4946,13 +4947,13 @@
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>288</v>
@@ -4983,7 +4984,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -4992,7 +4993,7 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>293</v>
@@ -5058,13 +5059,13 @@
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>297</v>
@@ -5095,7 +5096,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5104,7 +5105,7 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>302</v>
@@ -5172,13 +5173,13 @@
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>307</v>
@@ -5209,16 +5210,16 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>251</v>
@@ -5290,13 +5291,13 @@
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>316</v>
@@ -5336,7 +5337,7 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>185</v>
@@ -5412,7 +5413,7 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>328</v>
@@ -5421,7 +5422,7 @@
         <v>329</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>330</v>
@@ -5440,10 +5441,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5452,10 +5453,10 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>332</v>
@@ -5522,13 +5523,13 @@
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>336</v>
@@ -5571,7 +5572,7 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>340</v>
@@ -5644,7 +5645,7 @@
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
@@ -5907,7 +5908,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -5916,7 +5917,7 @@
         <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>302</v>
@@ -5984,13 +5985,13 @@
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>316</v>
@@ -5999,7 +6000,7 @@
         <v>370</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6106,13 +6107,13 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>377</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6123,10 +6124,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6137,7 +6138,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6149,13 +6150,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6206,13 +6207,13 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
@@ -6224,7 +6225,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6235,14 +6236,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6261,16 +6262,16 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6320,7 +6321,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6332,13 +6333,13 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6349,14 +6350,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6369,25 +6370,25 @@
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6436,7 +6437,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6448,13 +6449,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6465,10 +6466,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6479,7 +6480,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6494,14 +6495,14 @@
         <v>185</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6529,10 +6530,10 @@
         <v>190</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6550,25 +6551,25 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6579,10 +6580,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6593,7 +6594,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6605,17 +6606,17 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6664,25 +6665,25 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6693,10 +6694,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6722,14 +6723,14 @@
         <v>345</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6778,7 +6779,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6790,13 +6791,13 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6807,10 +6808,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6821,7 +6822,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6836,14 +6837,14 @@
         <v>356</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6892,25 +6893,25 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6921,10 +6922,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6947,17 +6948,17 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7006,7 +7007,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7018,13 +7019,13 @@
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="416">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -271,9 +271,6 @@
     <t>Organization(classCode=ORG, determinerCode=INST)</t>
   </si>
   <si>
-    <t>administrative.group</t>
-  </si>
-  <si>
     <t>Organization.id</t>
   </si>
   <si>
@@ -357,7 +354,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -415,10 +412,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -459,7 +452,7 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -519,6 +512,10 @@
     <t>Organization.identifier.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -574,7 +571,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.3.0</t>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -608,6 +608,9 @@
     <t>extensible</t>
   </si>
   <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
@@ -708,10 +711,6 @@
     <t>Organization.identifier.type.coding.version</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Version of the system - if relevant</t>
   </si>
   <si>
@@ -893,7 +892,7 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
@@ -1180,10 +1179,6 @@
   </si>
   <si>
     <t>Need to keep track of assigned contact points within bigger organization.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>.contactParty</t>
@@ -1633,7 +1628,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.10546875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="43.6484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -1881,15 +1876,15 @@
         <v>30</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1900,28 +1895,28 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1971,13 +1966,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -2000,10 +1995,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2014,25 +2009,25 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2083,19 +2078,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2112,10 +2107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2126,28 +2121,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2197,19 +2192,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2226,10 +2221,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2240,7 +2235,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2252,16 +2247,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2287,43 +2282,43 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2340,21 +2335,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2366,16 +2361,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>119</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2425,25 +2420,25 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2454,14 +2449,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2480,16 +2475,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2539,7 +2534,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2551,13 +2546,13 @@
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2568,14 +2563,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2594,16 +2589,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2653,7 +2648,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2665,13 +2660,13 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2682,14 +2677,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2702,25 +2697,25 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2769,7 +2764,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2781,13 +2776,13 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2798,10 +2793,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2809,7 +2804,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>79</v>
@@ -2821,20 +2816,20 @@
         <v>77</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2871,19 +2866,19 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="AC11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>152</v>
-      </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2892,65 +2887,65 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>157</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J12" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K12" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2999,7 +2994,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3008,30 +3003,30 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AJ12" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3042,7 +3037,7 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
@@ -3054,13 +3049,13 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3111,25 +3106,25 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3140,14 +3135,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3166,16 +3161,16 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3213,19 +3208,19 @@
         <v>77</v>
       </c>
       <c r="AB14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AC14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AC14" t="s" s="2">
+      <c r="AD14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AD14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE14" t="s" s="2">
+      <c r="AF14" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3237,13 +3232,13 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3254,10 +3249,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3268,31 +3263,31 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3317,9 +3312,11 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
         <v>180</v>
       </c>
@@ -3345,16 +3342,16 @@
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>182</v>
@@ -3382,16 +3379,16 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J16" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>185</v>
@@ -3433,9 +3430,11 @@
       <c r="X16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="Y16" s="2"/>
+      <c r="Y16" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3453,22 +3452,22 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>182</v>
@@ -3482,10 +3481,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3496,7 +3495,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3508,13 +3507,13 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3565,25 +3564,25 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL17" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3594,14 +3593,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3620,16 +3619,16 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3667,19 +3666,19 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AC18" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AC18" t="s" s="2">
+      <c r="AD18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AD18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE18" t="s" s="2">
+      <c r="AF18" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3691,13 +3690,13 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3708,10 +3707,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3731,22 +3730,22 @@
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3795,7 +3794,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3807,13 +3806,13 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3824,10 +3823,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3838,7 +3837,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -3850,13 +3849,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3907,25 +3906,25 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3936,14 +3935,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3962,16 +3961,16 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4009,19 +4008,19 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AC21" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AC21" t="s" s="2">
+      <c r="AD21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE21" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="AD21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE21" t="s" s="2">
+      <c r="AF21" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4033,13 +4032,13 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -4050,10 +4049,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4064,31 +4063,31 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4098,7 +4097,7 @@
         <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>77</v>
@@ -4137,25 +4136,25 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4166,10 +4165,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4180,19 +4179,19 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K23" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>225</v>
@@ -4257,13 +4256,13 @@
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>229</v>
@@ -4294,19 +4293,19 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>233</v>
@@ -4371,13 +4370,13 @@
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>238</v>
@@ -4408,19 +4407,19 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K25" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>242</v>
@@ -4485,13 +4484,13 @@
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>247</v>
@@ -4522,16 +4521,16 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>251</v>
@@ -4601,13 +4600,13 @@
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>257</v>
@@ -4638,19 +4637,19 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>261</v>
@@ -4717,13 +4716,13 @@
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>267</v>
@@ -4751,22 +4750,22 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J28" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G28" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K28" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>271</v>
@@ -4833,13 +4832,13 @@
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>278</v>
@@ -4867,22 +4866,22 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G29" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>283</v>
@@ -4947,13 +4946,13 @@
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>288</v>
@@ -4984,16 +4983,16 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>293</v>
@@ -5059,13 +5058,13 @@
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>297</v>
@@ -5096,16 +5095,16 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>302</v>
@@ -5173,13 +5172,13 @@
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>307</v>
@@ -5210,16 +5209,16 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I32" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>251</v>
@@ -5291,13 +5290,13 @@
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>316</v>
@@ -5337,7 +5336,7 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>185</v>
@@ -5413,7 +5412,7 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>328</v>
@@ -5422,7 +5421,7 @@
         <v>329</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>330</v>
@@ -5441,22 +5440,22 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J34" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G34" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="K34" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>332</v>
@@ -5523,13 +5522,13 @@
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>336</v>
@@ -5572,7 +5571,7 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>340</v>
@@ -5645,7 +5644,7 @@
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
@@ -5908,16 +5907,16 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
         <v>302</v>
@@ -5985,13 +5984,13 @@
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>316</v>
@@ -6000,7 +5999,7 @@
         <v>370</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6107,13 +6106,13 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6124,10 +6123,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6138,7 +6137,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6150,13 +6149,13 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6207,25 +6206,25 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6236,14 +6235,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6262,16 +6261,16 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>137</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6321,7 +6320,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6333,13 +6332,13 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6350,14 +6349,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6370,25 +6369,25 @@
         <v>77</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M42" t="s" s="2">
-        <v>384</v>
-      </c>
       <c r="N42" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6437,7 +6436,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6449,13 +6448,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6466,10 +6465,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6480,7 +6479,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6495,14 +6494,14 @@
         <v>185</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6530,46 +6529,46 @@
         <v>190</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z43" t="s" s="2">
+      <c r="AA43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6580,10 +6579,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6594,7 +6593,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>77</v>
@@ -6606,17 +6605,17 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6665,25 +6664,25 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6694,10 +6693,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6723,14 +6722,14 @@
         <v>345</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6779,7 +6778,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6791,13 +6790,13 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6808,10 +6807,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6822,7 +6821,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6837,14 +6836,14 @@
         <v>356</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6893,25 +6892,25 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -6922,10 +6921,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6948,17 +6947,17 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7007,7 +7006,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7019,13 +7018,13 @@
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>

--- a/branches/Richard/StructureDefinition-requesting-organization.xlsx
+++ b/branches/Richard/StructureDefinition-requesting-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
